--- a/data/wechat_shipment_log.xlsx
+++ b/data/wechat_shipment_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F806"/>
+  <dimension ref="A1:F895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26219,6 +26219,2854 @@
       <c r="F806" t="inlineStr">
         <is>
           <t>2026-03-12 08:22:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:15:00</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>99796中断vee12 a寸理是2深-c</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>99796</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>99796</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-03-11 17:15:00</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>99796</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>99796</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>99796</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-03-11 18:58:00</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>2+单99843台肺二一</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>99843</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>99843</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-03-11 18:58:00</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>99843</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>99843</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>99843</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-03-11 19:08:00</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>正共生99814:一一138一图…重文</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>99814</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>99814</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-03-11 19:08:00</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>99814</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>99814</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>99814</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-03-11 20:45:00</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>99168售后单号</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>99168</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>99168</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:14:00</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>99710-1-2</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>99710-1-2</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>99710</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>m99641-3:件es2 60格是画组2m”21青轩警阳</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>99641-3</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>99641</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>99641-3</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>99641-3</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>99641</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>99845D量-2-8仔细检查27105</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>99845</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>99845</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>99845D量-2-8仔细检查27105</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>27105</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>27105</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>99845</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>99845</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>99845</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>正常499818加nr放905x11家连·指a平二……mm</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>499818</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>499818</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>99818</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>99818</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>99818</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>M7-··.出948664重中册隐…国……T上8时些</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>948664</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>948664</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>99849</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>99849</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>99849</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>9984845na--通临m8</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>9984845</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>9984845</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>99848</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>99848</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>99848</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>99834-1!</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>99834-1</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>99834</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:29:00</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>99834-1-2-3</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>99834-1-2-3</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>99834</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:35:00</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>中谐霭99821-1:一3/11一站—-一一</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>99821-1</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>99821</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:35:00</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>99821-1-2-3</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>99821-1-2-3</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>99821</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:35:00</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>99591Tane件内容来套子不一样的醋里</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>99591</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>99591</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:35:00</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>99591</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>99591</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>99591</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:35:00</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>正常**99847件吧T*0inac店-二-第nm四二</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>99847</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>99847</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:35:00</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>99847</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>99847</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>99847</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:35:00</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>99844打解3</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>99844</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>99844</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:35:00</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>99844</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>99844</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>99844</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-03-11 22:00:00</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>99851</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>99851</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>99851</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-03-11 22:00:00</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>99851le</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>99851</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>99851</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-03-11 22:26:00</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>aR99807中通下健一/1度C51soC100ka程是=一=22…r一一年</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>99807</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>99807</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-03-11 22:26:00</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>99807</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>99807</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>99807</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-03-11 22:47:00</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>99725-2</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>99725-2</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>99725</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-03-11 22:47:00</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>99725-2n天革2M=一中影r</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>99725-2</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>99725</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-03-11 22:47:00</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>9982623您检查发6四田</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>9982623</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>9982623</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-03-11 22:47:00</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>99826</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>99826</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>99826</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-03-11 22:47:00</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>99823画r:妈标L4mm…中a一</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>99823</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>99823</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-03-11 22:47:00</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>99823少数看单</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>99823</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>99823</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-03-11 22:59:00</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>99824:性东通同色183中2--</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>99824</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>99824</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-03-11 22:59:00</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>99824</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>99824</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>99824</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:20:00</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>正意**99817下的10M四2-热T画mE</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>99817</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>99817</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:20:00</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>99817</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>99817</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>99817</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:20:00</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>正常99873加件Fn理s*110-80第=---画2-斜收立液卫表源文件：</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>99873</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>99873</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:20:00</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>99873</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>99873</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>99873</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:20:00</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>99876:3/色扣子直筒长裤图…酷”T</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>99876</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>99876</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:20:00</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>99876</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>99876</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>99876</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:25:00</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>99726下色扣子s1拍所</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>99726</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>99726</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:25:00</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>99726</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>99726</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>99726</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:25:00</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>99830:一各字号码不一2本布银一i一</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>99830</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>99830</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:25:00</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>99830</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>99830</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>99830</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:25:00</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>99896=1-25查发u三le实a多ai</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>99896</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>99896</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:25:00</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>99896</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>99896</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>99896</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:25:00</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>99852nE重贴壤+帽绳=--二一-一一</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>99852</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>99852</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:25:00</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>99852</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>99852</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>99852</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:31:00</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>99850度号码不一样</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>99850</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>99850</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:31:00</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>99850</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>99850</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>99850</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>99895</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>99895</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>99895</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>xu不是小杰D解9989578用本布有本布地18 L-E适二一查好再E□D</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>9989578</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>9989578</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>正常99820非件m3/1 ne**三-</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>99820</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>99820</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>99820</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>99820</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>99820</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>小杰xu不是中998640rM*1仔细检查发ram能-r-一</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>998640</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>998640</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>99864</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>99864</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>99864</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>99866-1:中游寄旧付一3/11序细检查发货代e</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>99866-1</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>99866</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>99866-1-2</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>99866-1-2</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>99866</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>xu不是小杰中语扫样99869-1付3/12·◎三细检查发货</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>99869-1</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>99869</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>99869-1-2</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>99869-1-2</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>99869</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>中通鲜99872-1子细检查发货二。二Ev一--—一年</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>99872-1</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>99872</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>99872-1-2</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>99872-1-2</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>99872</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>xu不是小杰9985883/E[maaWam细检查发货aTT 这大a</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>9985883</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>9985883</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>99858</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>99858</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>99858</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>99897一一学字领复梦露2x1-</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>99897</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>99897</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>99897</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>99897</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>99897</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>东仔99892.n2细检查发货”一一一一二</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>99892</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>99892</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>99892-1-2</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>99892-1-2</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>99892</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>1I检查好再发99888142事进</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>99888142</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>99888142</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>99888-1-2</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>99888-1-2</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>99888</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>99904侧骤二0一二m</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>99904</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>99904</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>99904</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>99904</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>99904</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>件99891位_一3/124g88子细检查发货-一</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>99891</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>99891</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>99891</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>99891</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>99891</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>出99854:199853一i疆二三</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>99854</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>99854</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>出99854:199853一i疆二三</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>199853</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>199853</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>99853/99854一起发</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>99853</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>99853</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>99853/99854一起发</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>99854</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>99854</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>打998561阳016u2南自边图色值：143b鱼造富户的年一一一</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>998561</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>998561</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:37:00</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>99856</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>99856</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>99856</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:49:00</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>正E禁99842中加件曲二3st图一一-一1</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>99842</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>99842</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-03-11 23:49:00</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>99842</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>99842</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>99842</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>vx_order_3.12.docx</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:48:06</t>
         </is>
       </c>
     </row>
@@ -26310,7 +29158,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -26335,7 +29183,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -26360,7 +29208,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -26385,7 +29233,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -26435,7 +29283,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -30510,7 +33358,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172">
@@ -31560,7 +34408,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
@@ -33060,7 +35908,7 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274">
@@ -33435,7 +36283,7 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289">
@@ -33460,7 +36308,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="290">
@@ -34985,7 +37833,7 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="351">
@@ -35235,7 +38083,7 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="361">
@@ -35410,7 +38258,7 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="368">
@@ -35460,7 +38308,7 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="370">
@@ -35485,7 +38333,7 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -35535,7 +38383,7 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="373">
@@ -35560,7 +38408,7 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="374">
@@ -35585,7 +38433,7 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="375">
@@ -35635,7 +38483,7 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="377">
@@ -35660,7 +38508,7 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="378">
@@ -35685,7 +38533,7 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="379">
@@ -35710,7 +38558,7 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380">
@@ -35785,7 +38633,7 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="383">
@@ -35860,7 +38708,7 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -35885,7 +38733,7 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -35960,7 +38808,7 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="390">
@@ -35985,7 +38833,7 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="391">
@@ -36010,7 +38858,7 @@
         </is>
       </c>
       <c r="E391" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="392">
@@ -36035,7 +38883,7 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="393">
@@ -36085,7 +38933,7 @@
         </is>
       </c>
       <c r="E394" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="395">
@@ -36110,7 +38958,7 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -36135,7 +38983,7 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
@@ -36160,7 +39008,7 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -36185,7 +39033,7 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="399">
@@ -36210,7 +39058,7 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="400">
@@ -36235,7 +39083,7 @@
         </is>
       </c>
       <c r="E400" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="401">
@@ -36260,7 +39108,7 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="402">
@@ -36285,7 +39133,7 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="403">
@@ -36310,7 +39158,7 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="404">
@@ -36335,7 +39183,7 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="405">
@@ -36360,7 +39208,7 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="406">
@@ -36385,7 +39233,7 @@
         </is>
       </c>
       <c r="E406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="407">
@@ -36410,7 +39258,7 @@
         </is>
       </c>
       <c r="E407" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="408">
@@ -36435,7 +39283,7 @@
         </is>
       </c>
       <c r="E408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -36460,7 +39308,7 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -36485,7 +39333,7 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -36510,7 +39358,7 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -36535,7 +39383,7 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -36560,7 +39408,7 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -36585,7 +39433,7 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -36610,7 +39458,7 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="416">
@@ -36635,7 +39483,7 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="417">
@@ -36660,7 +39508,7 @@
         </is>
       </c>
       <c r="E417" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -36685,7 +39533,7 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -36710,7 +39558,7 @@
         </is>
       </c>
       <c r="E419" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="420">
@@ -36735,7 +39583,7 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -36760,7 +39608,7 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -36785,7 +39633,7 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="423">
@@ -36810,7 +39658,7 @@
         </is>
       </c>
       <c r="E423" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="424">
@@ -36835,7 +39683,7 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="425">
@@ -36860,7 +39708,7 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="426">
@@ -36885,7 +39733,7 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
